--- a/public/assets/xls/biblos-import.xlsx
+++ b/public/assets/xls/biblos-import.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="41">
   <si>
     <t>products(3)</t>
   </si>
@@ -46,7 +46,7 @@
     <t>Kategorija</t>
   </si>
   <si>
-    <t>Slika</t>
+    <t>Slike</t>
   </si>
   <si>
     <t>Cijena</t>
@@ -76,32 +76,31 @@
     <t>Mjesto izdavanja</t>
   </si>
   <si>
-    <t>Pismo</t>
-  </si>
-  <si>
     <t>Uvez</t>
   </si>
   <si>
     <t>Godina izdavanja</t>
   </si>
   <si>
-    <t>Stanje</t>
+    <t>Jezik</t>
   </si>
   <si>
     <t>Status</t>
   </si>
   <si>
+    <t>Povezani proizvodi</t>
+  </si>
+  <si>
     <t>Michael Scott</t>
   </si>
   <si>
     <t>Plava Krava</t>
   </si>
   <si>
-    <t xml:space="preserve">Alkemičar 
-</t>
-  </si>
-  <si>
-    <t>PK40</t>
+    <t>Alkemičar 7</t>
+  </si>
+  <si>
+    <t>PK40666</t>
   </si>
   <si>
     <t>On čuva tajnu koja može značiti kraj svijeta. Istina: Nicholas Flamel rođen je 28. rujna 1330. godine u Parizu. Gotovo sedamsto godina kasnije još ga uvijek prati glas najvećeg alkemičara njegova doba. Priča se da spoznao tajnu vječnoga života. Svi spisi navode da je umro 1418. godine. Njegova je grobnica, međutim, prazna. Legenda: Nicholas Flamel je živ. No samo zahvaljujući eliksiru života što ga proizvodi već stoljećima. Tajna besmrtnosti skrivena je u Knjizi Abrahama Židova. Upadne li ta knjiga u krive ruke, svijet će biti uništen. Upravo je to ono čemu se doktor John Dee nada i što planira učiniti čim se knjige dokopa. Ljudski rod pojma neće imati što se događa sve dok ne budem prekasno. A ako je vjerovati proročanstvu, jedini u čijoj je moći da svijet spase od potpuna uništenja su blizanci Sophie i Josh Newman. Ponekad se legende obistine. A Sophie i Josh Newman naći će se usred jedne od najvećih legendi svih vremena. Iz pera neupitnog autoriteta s područja mitologije i folkloristike, Michaela Scotta, majstora fantastike i jednog od najuspješnijih suvremenih irskih pisaca, predstavljamo još jedan od od najljepših izdanaka svjetske književnosti za mlade. Prije svega čarobnu, nesvakidašnju priču o hrabrosti i odanosti na hrvatskome je ispripovjedila Marija Kostović, a naslovna ilustracija,preuzeta s originalnog izdanja, djelo je Michaela Wagnera.</t>
@@ -110,10 +109,10 @@
     <t>alkemicar-michael-scott</t>
   </si>
   <si>
-    <t>Književnost, Biblioteka Vjeverica</t>
-  </si>
-  <si>
-    <t>26.41</t>
+    <t>Beletristika, Publicistika</t>
+  </si>
+  <si>
+    <t>30</t>
   </si>
   <si>
     <t>22.14</t>
@@ -132,13 +131,10 @@
     <t>Zagreb</t>
   </si>
   <si>
-    <t>Latinica</t>
-  </si>
-  <si>
     <t>Tvrdi</t>
   </si>
   <si>
-    <t>Dobro</t>
+    <t>Hrvatski</t>
   </si>
 </sst>
 </file>
@@ -754,6 +750,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
+          <a:tabLst/>
           <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1100" u="none" kumimoji="0" normalizeH="0">
             <a:ln>
               <a:noFill/>
@@ -783,6 +780,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
+          <a:tabLst/>
           <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
             <a:ln>
               <a:noFill/>
@@ -808,6 +806,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
+          <a:tabLst/>
           <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
             <a:ln>
               <a:noFill/>
@@ -833,6 +832,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
+          <a:tabLst/>
           <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
             <a:ln>
               <a:noFill/>
@@ -858,6 +858,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
+          <a:tabLst/>
           <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
             <a:ln>
               <a:noFill/>
@@ -883,6 +884,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
+          <a:tabLst/>
           <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
             <a:ln>
               <a:noFill/>
@@ -908,6 +910,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
+          <a:tabLst/>
           <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
             <a:ln>
               <a:noFill/>
@@ -933,6 +936,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
+          <a:tabLst/>
           <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
             <a:ln>
               <a:noFill/>
@@ -958,6 +962,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
+          <a:tabLst/>
           <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
             <a:ln>
               <a:noFill/>
@@ -983,6 +988,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
+          <a:tabLst/>
           <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
             <a:ln>
               <a:noFill/>
@@ -1033,6 +1039,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
+          <a:tabLst/>
           <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
             <a:ln>
               <a:noFill/>
@@ -1058,6 +1065,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
+          <a:tabLst/>
           <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
             <a:ln>
               <a:noFill/>
@@ -1083,6 +1091,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
+          <a:tabLst/>
           <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
             <a:ln>
               <a:noFill/>
@@ -1108,6 +1117,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
+          <a:tabLst/>
           <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
             <a:ln>
               <a:noFill/>
@@ -1133,6 +1143,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
+          <a:tabLst/>
           <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
             <a:ln>
               <a:noFill/>
@@ -1158,6 +1169,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
+          <a:tabLst/>
           <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
             <a:ln>
               <a:noFill/>
@@ -1183,6 +1195,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
+          <a:tabLst/>
           <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
             <a:ln>
               <a:noFill/>
@@ -1208,6 +1221,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
+          <a:tabLst/>
           <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
             <a:ln>
               <a:noFill/>
@@ -1233,6 +1247,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
+          <a:tabLst/>
           <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
             <a:ln>
               <a:noFill/>
@@ -1258,6 +1273,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
+          <a:tabLst/>
           <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
             <a:ln>
               <a:noFill/>
@@ -1305,6 +1321,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
+          <a:tabLst/>
           <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1100" u="none" kumimoji="0" normalizeH="0">
             <a:ln>
               <a:noFill/>
@@ -1334,6 +1351,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
+          <a:tabLst/>
           <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
             <a:ln>
               <a:noFill/>
@@ -1359,6 +1377,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
+          <a:tabLst/>
           <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
             <a:ln>
               <a:noFill/>
@@ -1384,6 +1403,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
+          <a:tabLst/>
           <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
             <a:ln>
               <a:noFill/>
@@ -1409,6 +1429,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
+          <a:tabLst/>
           <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
             <a:ln>
               <a:noFill/>
@@ -1434,6 +1455,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
+          <a:tabLst/>
           <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
             <a:ln>
               <a:noFill/>
@@ -1459,6 +1481,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
+          <a:tabLst/>
           <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
             <a:ln>
               <a:noFill/>
@@ -1484,6 +1507,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
+          <a:tabLst/>
           <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
             <a:ln>
               <a:noFill/>
@@ -1509,6 +1533,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
+          <a:tabLst/>
           <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
             <a:ln>
               <a:noFill/>
@@ -1534,6 +1559,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
+          <a:tabLst/>
           <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
             <a:ln>
               <a:noFill/>
@@ -1584,11 +1610,11 @@
     <col min="18" max="18" width="19.5" style="1" customWidth="1"/>
     <col min="19" max="19" width="13.6719" style="1" customWidth="1"/>
     <col min="20" max="20" width="16.5" style="1" customWidth="1"/>
-    <col min="21" max="21" width="13" style="1" customWidth="1"/>
-    <col min="22" max="22" width="12.3516" style="1" customWidth="1"/>
-    <col min="23" max="23" width="11" style="1" customWidth="1"/>
-    <col min="24" max="24" width="17.3516" style="1" customWidth="1"/>
-    <col min="25" max="25" width="18.6719" style="1" customWidth="1"/>
+    <col min="21" max="21" width="12.3516" style="1" customWidth="1"/>
+    <col min="22" max="22" width="11" style="1" customWidth="1"/>
+    <col min="23" max="23" width="17.3516" style="1" customWidth="1"/>
+    <col min="24" max="24" width="18.6719" style="1" customWidth="1"/>
+    <col min="25" max="25" width="27.3516" style="1" customWidth="1"/>
     <col min="26" max="16384" width="8.35156" style="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1732,7 +1758,7 @@
         <v>33</v>
       </c>
       <c r="M3" s="10">
-        <v>1</v>
+        <v>203</v>
       </c>
       <c r="N3" s="10">
         <v>5</v>
@@ -1758,18 +1784,14 @@
       <c r="U3" t="s" s="8">
         <v>39</v>
       </c>
-      <c r="V3" t="s" s="8">
+      <c r="V3" s="10">
+        <v>2021</v>
+      </c>
+      <c r="W3" t="s" s="8">
         <v>40</v>
       </c>
-      <c r="W3" s="10">
-        <v>2021</v>
-      </c>
-      <c r="X3" t="s" s="8">
-        <v>41</v>
-      </c>
-      <c r="Y3" s="10">
-        <v>0</v>
-      </c>
+      <c r="X3" s="11"/>
+      <c r="Y3" s="8"/>
     </row>
     <row r="4" ht="14.7" customHeight="1">
       <c r="A4" s="12"/>
@@ -1962,7 +1984,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:Y1"/>
+    <mergeCell ref="A1:X1"/>
   </mergeCells>
   <pageMargins left="1" right="1" top="1" bottom="1" header="0.25" footer="0.25"/>
   <pageSetup firstPageNumber="1" fitToHeight="1" fitToWidth="1" scale="100" useFirstPageNumber="0" orientation="portrait" pageOrder="downThenOver"/>
